--- a/data/raw/관세청/Import Export Performance by Commodity and Country(GW)/Soybean Oil/1507.10/Food use (.1000)/Brazil.xlsx
+++ b/data/raw/관세청/Import Export Performance by Commodity and Country(GW)/Soybean Oil/1507.10/Food use (.1000)/Brazil.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\데이터플랫폼팀\00 데이터플랫폼팀_공유\데이터플랫폼팀(23.03~)\08 데이터 분석\00 분석과제정의서\☆구매\수입원료\대두유\데이터\외부\경제, 무역\관세청\9개년_품목별 국가별 수출입실적\대두유\1507.10\식품용(.1000)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\데이터플랫폼팀\00 데이터플랫폼팀_공유\데이터플랫폼팀(23.03~)\08 데이터 분석\00 분석과제정의서\☆구매\수입원료\대두유\데이터\외부\경제, 무역\관세청\15개년_품목별 국가별 수출입실적\대두유\1507.10\식품용(.1000)\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25125" windowHeight="11640" firstSheet="4" activeTab="16"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25125" windowHeight="11640"/>
   </bookViews>
   <sheets>
     <sheet name="2010년" sheetId="10" r:id="rId1"/>
@@ -858,18 +858,10 @@
         <f t="shared" ref="B3:B14" si="0">C3-E3</f>
         <v>0</v>
       </c>
-      <c r="C3" s="2">
-        <v>0</v>
-      </c>
-      <c r="D3" s="2">
-        <v>0</v>
-      </c>
-      <c r="E3" s="2">
-        <v>0</v>
-      </c>
-      <c r="F3" s="2">
-        <v>0</v>
-      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -879,18 +871,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C4" s="2">
-        <v>0</v>
-      </c>
-      <c r="D4" s="2">
-        <v>0</v>
-      </c>
-      <c r="E4" s="2">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2">
-        <v>0</v>
-      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
@@ -900,18 +884,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C5" s="2">
-        <v>0</v>
-      </c>
-      <c r="D5" s="2">
-        <v>0</v>
-      </c>
-      <c r="E5" s="2">
-        <v>0</v>
-      </c>
-      <c r="F5" s="2">
-        <v>0</v>
-      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
@@ -921,18 +897,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C6" s="2">
-        <v>0</v>
-      </c>
-      <c r="D6" s="2">
-        <v>0</v>
-      </c>
-      <c r="E6" s="2">
-        <v>0</v>
-      </c>
-      <c r="F6" s="2">
-        <v>0</v>
-      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
@@ -942,18 +910,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C7" s="2">
-        <v>0</v>
-      </c>
-      <c r="D7" s="2">
-        <v>0</v>
-      </c>
-      <c r="E7" s="2">
-        <v>0</v>
-      </c>
-      <c r="F7" s="2">
-        <v>0</v>
-      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
@@ -963,18 +923,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C8" s="2">
-        <v>0</v>
-      </c>
-      <c r="D8" s="2">
-        <v>0</v>
-      </c>
-      <c r="E8" s="2">
-        <v>0</v>
-      </c>
-      <c r="F8" s="2">
-        <v>0</v>
-      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
@@ -984,18 +936,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C9" s="2">
-        <v>0</v>
-      </c>
-      <c r="D9" s="2">
-        <v>0</v>
-      </c>
-      <c r="E9" s="2">
-        <v>0</v>
-      </c>
-      <c r="F9" s="2">
-        <v>0</v>
-      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
@@ -1005,18 +949,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C10" s="2">
-        <v>0</v>
-      </c>
-      <c r="D10" s="2">
-        <v>0</v>
-      </c>
-      <c r="E10" s="2">
-        <v>0</v>
-      </c>
-      <c r="F10" s="2">
-        <v>0</v>
-      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
@@ -1026,18 +962,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C11" s="2">
-        <v>0</v>
-      </c>
-      <c r="D11" s="2">
-        <v>0</v>
-      </c>
-      <c r="E11" s="2">
-        <v>0</v>
-      </c>
-      <c r="F11" s="2">
-        <v>0</v>
-      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
@@ -1047,18 +975,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C12" s="2">
-        <v>0</v>
-      </c>
-      <c r="D12" s="2">
-        <v>0</v>
-      </c>
-      <c r="E12" s="2">
-        <v>0</v>
-      </c>
-      <c r="F12" s="2">
-        <v>0</v>
-      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
@@ -1068,18 +988,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C13" s="2">
-        <v>0</v>
-      </c>
-      <c r="D13" s="2">
-        <v>0</v>
-      </c>
-      <c r="E13" s="2">
-        <v>0</v>
-      </c>
-      <c r="F13" s="2">
-        <v>0</v>
-      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
@@ -1089,18 +1001,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C14" s="2">
-        <v>0</v>
-      </c>
-      <c r="D14" s="2">
-        <v>0</v>
-      </c>
-      <c r="E14" s="2">
-        <v>0</v>
-      </c>
-      <c r="F14" s="2">
-        <v>0</v>
-      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
     </row>
     <row r="15" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
@@ -1170,18 +1074,10 @@
         <f t="shared" ref="B3:B14" si="0">C3-E3</f>
         <v>0</v>
       </c>
-      <c r="C3" s="2">
-        <v>0</v>
-      </c>
-      <c r="D3" s="2">
-        <v>0</v>
-      </c>
-      <c r="E3" s="2">
-        <v>0</v>
-      </c>
-      <c r="F3" s="2">
-        <v>0</v>
-      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -1191,18 +1087,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C4" s="2">
-        <v>0</v>
-      </c>
-      <c r="D4" s="2">
-        <v>0</v>
-      </c>
-      <c r="E4" s="2">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2">
-        <v>0</v>
-      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
@@ -1212,18 +1100,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C5" s="2">
-        <v>0</v>
-      </c>
-      <c r="D5" s="2">
-        <v>0</v>
-      </c>
-      <c r="E5" s="2">
-        <v>0</v>
-      </c>
-      <c r="F5" s="2">
-        <v>0</v>
-      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
@@ -1233,18 +1113,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C6" s="2">
-        <v>0</v>
-      </c>
-      <c r="D6" s="2">
-        <v>0</v>
-      </c>
-      <c r="E6" s="2">
-        <v>0</v>
-      </c>
-      <c r="F6" s="2">
-        <v>0</v>
-      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
@@ -1254,18 +1126,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C7" s="2">
-        <v>0</v>
-      </c>
-      <c r="D7" s="2">
-        <v>0</v>
-      </c>
-      <c r="E7" s="2">
-        <v>0</v>
-      </c>
-      <c r="F7" s="2">
-        <v>0</v>
-      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
@@ -1275,18 +1139,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C8" s="2">
-        <v>0</v>
-      </c>
-      <c r="D8" s="2">
-        <v>0</v>
-      </c>
-      <c r="E8" s="2">
-        <v>0</v>
-      </c>
-      <c r="F8" s="2">
-        <v>0</v>
-      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
@@ -1296,18 +1152,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C9" s="2">
-        <v>0</v>
-      </c>
-      <c r="D9" s="2">
-        <v>0</v>
-      </c>
-      <c r="E9" s="2">
-        <v>0</v>
-      </c>
-      <c r="F9" s="2">
-        <v>0</v>
-      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
@@ -1317,18 +1165,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C10" s="2">
-        <v>0</v>
-      </c>
-      <c r="D10" s="2">
-        <v>0</v>
-      </c>
-      <c r="E10" s="2">
-        <v>0</v>
-      </c>
-      <c r="F10" s="2">
-        <v>0</v>
-      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
@@ -1338,18 +1178,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C11" s="2">
-        <v>0</v>
-      </c>
-      <c r="D11" s="2">
-        <v>0</v>
-      </c>
-      <c r="E11" s="2">
-        <v>0</v>
-      </c>
-      <c r="F11" s="2">
-        <v>0</v>
-      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
@@ -1359,18 +1191,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C12" s="2">
-        <v>0</v>
-      </c>
-      <c r="D12" s="2">
-        <v>0</v>
-      </c>
-      <c r="E12" s="2">
-        <v>0</v>
-      </c>
-      <c r="F12" s="2">
-        <v>0</v>
-      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
@@ -1380,18 +1204,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C13" s="2">
-        <v>0</v>
-      </c>
-      <c r="D13" s="2">
-        <v>0</v>
-      </c>
-      <c r="E13" s="2">
-        <v>0</v>
-      </c>
-      <c r="F13" s="2">
-        <v>0</v>
-      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
@@ -1401,18 +1217,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C14" s="2">
-        <v>0</v>
-      </c>
-      <c r="D14" s="2">
-        <v>0</v>
-      </c>
-      <c r="E14" s="2">
-        <v>0</v>
-      </c>
-      <c r="F14" s="2">
-        <v>0</v>
-      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
     </row>
     <row r="15" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
@@ -1503,18 +1311,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C4" s="2">
-        <v>0</v>
-      </c>
-      <c r="D4" s="2">
-        <v>0</v>
-      </c>
-      <c r="E4" s="2">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2">
-        <v>0</v>
-      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
@@ -1524,18 +1324,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C5" s="2">
-        <v>0</v>
-      </c>
-      <c r="D5" s="2">
-        <v>0</v>
-      </c>
-      <c r="E5" s="2">
-        <v>0</v>
-      </c>
-      <c r="F5" s="2">
-        <v>0</v>
-      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
@@ -1545,18 +1337,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C6" s="2">
-        <v>0</v>
-      </c>
-      <c r="D6" s="2">
-        <v>0</v>
-      </c>
-      <c r="E6" s="2">
-        <v>0</v>
-      </c>
-      <c r="F6" s="2">
-        <v>0</v>
-      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
@@ -1566,18 +1350,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C7" s="2">
-        <v>0</v>
-      </c>
-      <c r="D7" s="2">
-        <v>0</v>
-      </c>
-      <c r="E7" s="2">
-        <v>0</v>
-      </c>
-      <c r="F7" s="2">
-        <v>0</v>
-      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
@@ -1671,18 +1447,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C12" s="2">
-        <v>0</v>
-      </c>
-      <c r="D12" s="2">
-        <v>0</v>
-      </c>
-      <c r="E12" s="2">
-        <v>0</v>
-      </c>
-      <c r="F12" s="2">
-        <v>0</v>
-      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
@@ -1692,18 +1460,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C13" s="2">
-        <v>0</v>
-      </c>
-      <c r="D13" s="2">
-        <v>0</v>
-      </c>
-      <c r="E13" s="2">
-        <v>0</v>
-      </c>
-      <c r="F13" s="2">
-        <v>0</v>
-      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
@@ -1713,18 +1473,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C14" s="2">
-        <v>0</v>
-      </c>
-      <c r="D14" s="2">
-        <v>0</v>
-      </c>
-      <c r="E14" s="2">
-        <v>0</v>
-      </c>
-      <c r="F14" s="2">
-        <v>0</v>
-      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
     </row>
     <row r="15" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
@@ -1794,18 +1546,10 @@
         <f t="shared" ref="B3:B14" si="0">C3-E3</f>
         <v>0</v>
       </c>
-      <c r="C3" s="2">
-        <v>0</v>
-      </c>
-      <c r="D3" s="2">
-        <v>0</v>
-      </c>
-      <c r="E3" s="2">
-        <v>0</v>
-      </c>
-      <c r="F3" s="2">
-        <v>0</v>
-      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -1815,18 +1559,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C4" s="2">
-        <v>0</v>
-      </c>
-      <c r="D4" s="2">
-        <v>0</v>
-      </c>
-      <c r="E4" s="2">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2">
-        <v>0</v>
-      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
@@ -1836,18 +1572,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C5" s="2">
-        <v>0</v>
-      </c>
-      <c r="D5" s="2">
-        <v>0</v>
-      </c>
-      <c r="E5" s="2">
-        <v>0</v>
-      </c>
-      <c r="F5" s="2">
-        <v>0</v>
-      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
@@ -1857,18 +1585,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C6" s="2">
-        <v>0</v>
-      </c>
-      <c r="D6" s="2">
-        <v>0</v>
-      </c>
-      <c r="E6" s="2">
-        <v>0</v>
-      </c>
-      <c r="F6" s="2">
-        <v>0</v>
-      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
@@ -1878,18 +1598,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C7" s="2">
-        <v>0</v>
-      </c>
-      <c r="D7" s="2">
-        <v>0</v>
-      </c>
-      <c r="E7" s="2">
-        <v>0</v>
-      </c>
-      <c r="F7" s="2">
-        <v>0</v>
-      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
@@ -1899,18 +1611,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C8" s="2">
-        <v>0</v>
-      </c>
-      <c r="D8" s="2">
-        <v>0</v>
-      </c>
-      <c r="E8" s="2">
-        <v>0</v>
-      </c>
-      <c r="F8" s="2">
-        <v>0</v>
-      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
@@ -2025,18 +1729,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C14" s="2">
-        <v>0</v>
-      </c>
-      <c r="D14" s="2">
-        <v>0</v>
-      </c>
-      <c r="E14" s="2">
-        <v>0</v>
-      </c>
-      <c r="F14" s="2">
-        <v>0</v>
-      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
     </row>
     <row r="15" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
@@ -2127,18 +1823,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C4" s="2">
-        <v>0</v>
-      </c>
-      <c r="D4" s="2">
-        <v>0</v>
-      </c>
-      <c r="E4" s="2">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2">
-        <v>0</v>
-      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
@@ -2169,18 +1857,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C6" s="2">
-        <v>0</v>
-      </c>
-      <c r="D6" s="2">
-        <v>0</v>
-      </c>
-      <c r="E6" s="2">
-        <v>0</v>
-      </c>
-      <c r="F6" s="2">
-        <v>0</v>
-      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
@@ -2190,18 +1870,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C7" s="2">
-        <v>0</v>
-      </c>
-      <c r="D7" s="2">
-        <v>0</v>
-      </c>
-      <c r="E7" s="2">
-        <v>0</v>
-      </c>
-      <c r="F7" s="2">
-        <v>0</v>
-      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
@@ -2232,18 +1904,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C9" s="2">
-        <v>0</v>
-      </c>
-      <c r="D9" s="2">
-        <v>0</v>
-      </c>
-      <c r="E9" s="2">
-        <v>0</v>
-      </c>
-      <c r="F9" s="2">
-        <v>0</v>
-      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
@@ -2274,18 +1938,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C11" s="2">
-        <v>0</v>
-      </c>
-      <c r="D11" s="2">
-        <v>0</v>
-      </c>
-      <c r="E11" s="2">
-        <v>0</v>
-      </c>
-      <c r="F11" s="2">
-        <v>0</v>
-      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
@@ -2295,18 +1951,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C12" s="2">
-        <v>0</v>
-      </c>
-      <c r="D12" s="2">
-        <v>0</v>
-      </c>
-      <c r="E12" s="2">
-        <v>0</v>
-      </c>
-      <c r="F12" s="2">
-        <v>0</v>
-      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
@@ -2316,18 +1964,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C13" s="2">
-        <v>0</v>
-      </c>
-      <c r="D13" s="2">
-        <v>0</v>
-      </c>
-      <c r="E13" s="2">
-        <v>0</v>
-      </c>
-      <c r="F13" s="2">
-        <v>0</v>
-      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
@@ -2337,18 +1977,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C14" s="2">
-        <v>0</v>
-      </c>
-      <c r="D14" s="2">
-        <v>0</v>
-      </c>
-      <c r="E14" s="2">
-        <v>0</v>
-      </c>
-      <c r="F14" s="2">
-        <v>0</v>
-      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
     </row>
     <row r="15" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
@@ -2439,18 +2071,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C4" s="2">
-        <v>0</v>
-      </c>
-      <c r="D4" s="2">
-        <v>0</v>
-      </c>
-      <c r="E4" s="2">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2">
-        <v>0</v>
-      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
@@ -2460,18 +2084,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C5" s="2">
-        <v>0</v>
-      </c>
-      <c r="D5" s="2">
-        <v>0</v>
-      </c>
-      <c r="E5" s="2">
-        <v>0</v>
-      </c>
-      <c r="F5" s="2">
-        <v>0</v>
-      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
@@ -2565,18 +2181,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C10" s="2">
-        <v>0</v>
-      </c>
-      <c r="D10" s="2">
-        <v>0</v>
-      </c>
-      <c r="E10" s="2">
-        <v>0</v>
-      </c>
-      <c r="F10" s="2">
-        <v>0</v>
-      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
@@ -2586,18 +2194,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C11" s="2">
-        <v>0</v>
-      </c>
-      <c r="D11" s="2">
-        <v>0</v>
-      </c>
-      <c r="E11" s="2">
-        <v>0</v>
-      </c>
-      <c r="F11" s="2">
-        <v>0</v>
-      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
@@ -2628,18 +2228,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C13" s="2">
-        <v>0</v>
-      </c>
-      <c r="D13" s="2">
-        <v>0</v>
-      </c>
-      <c r="E13" s="2">
-        <v>0</v>
-      </c>
-      <c r="F13" s="2">
-        <v>0</v>
-      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
@@ -2649,18 +2241,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C14" s="2">
-        <v>0</v>
-      </c>
-      <c r="D14" s="2">
-        <v>0</v>
-      </c>
-      <c r="E14" s="2">
-        <v>0</v>
-      </c>
-      <c r="F14" s="2">
-        <v>0</v>
-      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
     </row>
     <row r="15" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
@@ -2691,6 +2275,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2730,18 +2315,10 @@
         <f t="shared" ref="B3:B14" si="0">C3-E3</f>
         <v>0</v>
       </c>
-      <c r="C3" s="2">
-        <v>0</v>
-      </c>
-      <c r="D3" s="2">
-        <v>0</v>
-      </c>
-      <c r="E3" s="2">
-        <v>0</v>
-      </c>
-      <c r="F3" s="2">
-        <v>0</v>
-      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -2751,18 +2328,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C4" s="2">
-        <v>0</v>
-      </c>
-      <c r="D4" s="2">
-        <v>0</v>
-      </c>
-      <c r="E4" s="2">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2">
-        <v>0</v>
-      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
@@ -2772,18 +2341,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C5" s="2">
-        <v>0</v>
-      </c>
-      <c r="D5" s="2">
-        <v>0</v>
-      </c>
-      <c r="E5" s="2">
-        <v>0</v>
-      </c>
-      <c r="F5" s="2">
-        <v>0</v>
-      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
@@ -2793,18 +2354,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C6" s="2">
-        <v>0</v>
-      </c>
-      <c r="D6" s="2">
-        <v>0</v>
-      </c>
-      <c r="E6" s="2">
-        <v>0</v>
-      </c>
-      <c r="F6" s="2">
-        <v>0</v>
-      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
@@ -2814,18 +2367,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C7" s="2">
-        <v>0</v>
-      </c>
-      <c r="D7" s="2">
-        <v>0</v>
-      </c>
-      <c r="E7" s="2">
-        <v>0</v>
-      </c>
-      <c r="F7" s="2">
-        <v>0</v>
-      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
@@ -2835,18 +2380,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C8" s="2">
-        <v>0</v>
-      </c>
-      <c r="D8" s="2">
-        <v>0</v>
-      </c>
-      <c r="E8" s="2">
-        <v>0</v>
-      </c>
-      <c r="F8" s="2">
-        <v>0</v>
-      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
@@ -2919,18 +2456,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C12" s="2">
-        <v>0</v>
-      </c>
-      <c r="D12" s="2">
-        <v>0</v>
-      </c>
-      <c r="E12" s="2">
-        <v>0</v>
-      </c>
-      <c r="F12" s="2">
-        <v>0</v>
-      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
@@ -2940,18 +2469,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C13" s="2">
-        <v>0</v>
-      </c>
-      <c r="D13" s="2">
-        <v>0</v>
-      </c>
-      <c r="E13" s="2">
-        <v>0</v>
-      </c>
-      <c r="F13" s="2">
-        <v>0</v>
-      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
@@ -2961,18 +2482,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C14" s="2">
-        <v>0</v>
-      </c>
-      <c r="D14" s="2">
-        <v>0</v>
-      </c>
-      <c r="E14" s="2">
-        <v>0</v>
-      </c>
-      <c r="F14" s="2">
-        <v>0</v>
-      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
     </row>
     <row r="15" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
@@ -4723,18 +4236,10 @@
         <f t="shared" ref="B3:B8" si="0">C3-E3</f>
         <v>0</v>
       </c>
-      <c r="C3" s="2">
-        <v>0</v>
-      </c>
-      <c r="D3" s="2">
-        <v>0</v>
-      </c>
-      <c r="E3" s="2">
-        <v>0</v>
-      </c>
-      <c r="F3" s="2">
-        <v>0</v>
-      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -4744,18 +4249,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C4" s="2">
-        <v>0</v>
-      </c>
-      <c r="D4" s="2">
-        <v>0</v>
-      </c>
-      <c r="E4" s="2">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2">
-        <v>0</v>
-      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
@@ -4765,18 +4262,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C5" s="2">
-        <v>0</v>
-      </c>
-      <c r="D5" s="2">
-        <v>0</v>
-      </c>
-      <c r="E5" s="2">
-        <v>0</v>
-      </c>
-      <c r="F5" s="2">
-        <v>0</v>
-      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
@@ -4786,18 +4275,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C6" s="2">
-        <v>0</v>
-      </c>
-      <c r="D6" s="2">
-        <v>0</v>
-      </c>
-      <c r="E6" s="2">
-        <v>0</v>
-      </c>
-      <c r="F6" s="2">
-        <v>0</v>
-      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
@@ -4807,18 +4288,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C7" s="2">
-        <v>0</v>
-      </c>
-      <c r="D7" s="2">
-        <v>0</v>
-      </c>
-      <c r="E7" s="2">
-        <v>0</v>
-      </c>
-      <c r="F7" s="2">
-        <v>0</v>
-      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
@@ -4828,18 +4301,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C8" s="2">
-        <v>0</v>
-      </c>
-      <c r="D8" s="2">
-        <v>0</v>
-      </c>
-      <c r="E8" s="2">
-        <v>0</v>
-      </c>
-      <c r="F8" s="2">
-        <v>0</v>
-      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
@@ -4870,18 +4335,10 @@
         <f t="shared" ref="B10:B14" si="1">C10-E10</f>
         <v>0</v>
       </c>
-      <c r="C10" s="2">
-        <v>0</v>
-      </c>
-      <c r="D10" s="2">
-        <v>0</v>
-      </c>
-      <c r="E10" s="2">
-        <v>0</v>
-      </c>
-      <c r="F10" s="2">
-        <v>0</v>
-      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
@@ -4891,18 +4348,10 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="C11" s="2">
-        <v>0</v>
-      </c>
-      <c r="D11" s="2">
-        <v>0</v>
-      </c>
-      <c r="E11" s="2">
-        <v>0</v>
-      </c>
-      <c r="F11" s="2">
-        <v>0</v>
-      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
@@ -4912,18 +4361,10 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="C12" s="2">
-        <v>0</v>
-      </c>
-      <c r="D12" s="2">
-        <v>0</v>
-      </c>
-      <c r="E12" s="2">
-        <v>0</v>
-      </c>
-      <c r="F12" s="2">
-        <v>0</v>
-      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
@@ -4933,18 +4374,10 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="C13" s="2">
-        <v>0</v>
-      </c>
-      <c r="D13" s="2">
-        <v>0</v>
-      </c>
-      <c r="E13" s="2">
-        <v>0</v>
-      </c>
-      <c r="F13" s="2">
-        <v>0</v>
-      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
@@ -4954,41 +4387,33 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="C14" s="2">
-        <v>0</v>
-      </c>
-      <c r="D14" s="2">
-        <v>0</v>
-      </c>
-      <c r="E14" s="2">
-        <v>0</v>
-      </c>
-      <c r="F14" s="2">
-        <v>0</v>
-      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
     </row>
     <row r="15" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B15" s="5">
-        <f t="shared" ref="B15" si="2">E15-C15</f>
+        <f>SUM(B3:B14)</f>
+        <v>-18874</v>
+      </c>
+      <c r="C15" s="5">
+        <f t="shared" ref="C15:F15" si="2">SUM(C3:C14)</f>
+        <v>0</v>
+      </c>
+      <c r="D15" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E15" s="5">
+        <f t="shared" si="2"/>
         <v>18874</v>
       </c>
-      <c r="C15" s="5">
-        <f t="shared" ref="C15" si="3">SUM(C3:C14)</f>
-        <v>0</v>
-      </c>
-      <c r="D15" s="5">
-        <f t="shared" ref="D15" si="4">SUM(D3:D14)</f>
-        <v>0</v>
-      </c>
-      <c r="E15" s="5">
-        <f t="shared" ref="E15:F15" si="5">SUM(E3:E14)</f>
-        <v>18874</v>
-      </c>
       <c r="F15" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>21820</v>
       </c>
     </row>
@@ -5035,18 +4460,10 @@
         <f>C3-E3</f>
         <v>0</v>
       </c>
-      <c r="C3" s="2">
-        <v>0</v>
-      </c>
-      <c r="D3" s="2">
-        <v>0</v>
-      </c>
-      <c r="E3" s="2">
-        <v>0</v>
-      </c>
-      <c r="F3" s="2">
-        <v>0</v>
-      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -5056,18 +4473,10 @@
         <f t="shared" ref="B4:B14" si="0">C4-E4</f>
         <v>0</v>
       </c>
-      <c r="C4" s="2">
-        <v>0</v>
-      </c>
-      <c r="D4" s="2">
-        <v>0</v>
-      </c>
-      <c r="E4" s="2">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2">
-        <v>0</v>
-      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
@@ -5077,18 +4486,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C5" s="2">
-        <v>0</v>
-      </c>
-      <c r="D5" s="2">
-        <v>0</v>
-      </c>
-      <c r="E5" s="2">
-        <v>0</v>
-      </c>
-      <c r="F5" s="2">
-        <v>0</v>
-      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
@@ -5098,18 +4499,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C6" s="2">
-        <v>0</v>
-      </c>
-      <c r="D6" s="2">
-        <v>0</v>
-      </c>
-      <c r="E6" s="2">
-        <v>0</v>
-      </c>
-      <c r="F6" s="2">
-        <v>0</v>
-      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
@@ -5119,18 +4512,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C7" s="2">
-        <v>0</v>
-      </c>
-      <c r="D7" s="2">
-        <v>0</v>
-      </c>
-      <c r="E7" s="2">
-        <v>0</v>
-      </c>
-      <c r="F7" s="2">
-        <v>0</v>
-      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
@@ -5140,18 +4525,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C8" s="2">
-        <v>0</v>
-      </c>
-      <c r="D8" s="2">
-        <v>0</v>
-      </c>
-      <c r="E8" s="2">
-        <v>0</v>
-      </c>
-      <c r="F8" s="2">
-        <v>0</v>
-      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
@@ -5161,18 +4538,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C9" s="2">
-        <v>0</v>
-      </c>
-      <c r="D9" s="2">
-        <v>0</v>
-      </c>
-      <c r="E9" s="2">
-        <v>0</v>
-      </c>
-      <c r="F9" s="2">
-        <v>0</v>
-      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
@@ -5203,18 +4572,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C11" s="2">
-        <v>0</v>
-      </c>
-      <c r="D11" s="2">
-        <v>0</v>
-      </c>
-      <c r="E11" s="2">
-        <v>0</v>
-      </c>
-      <c r="F11" s="2">
-        <v>0</v>
-      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
@@ -5224,18 +4585,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C12" s="2">
-        <v>0</v>
-      </c>
-      <c r="D12" s="2">
-        <v>0</v>
-      </c>
-      <c r="E12" s="2">
-        <v>0</v>
-      </c>
-      <c r="F12" s="2">
-        <v>0</v>
-      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
@@ -5245,18 +4598,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C13" s="2">
-        <v>0</v>
-      </c>
-      <c r="D13" s="2">
-        <v>0</v>
-      </c>
-      <c r="E13" s="2">
-        <v>0</v>
-      </c>
-      <c r="F13" s="2">
-        <v>0</v>
-      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
@@ -5266,18 +4611,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C14" s="2">
-        <v>0</v>
-      </c>
-      <c r="D14" s="2">
-        <v>0</v>
-      </c>
-      <c r="E14" s="2">
-        <v>0</v>
-      </c>
-      <c r="F14" s="2">
-        <v>0</v>
-      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
     </row>
     <row r="15" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
